--- a/cleansheet/tests/fixtures/expected/romanian_contacts_cleaned.xlsx
+++ b/cleansheet/tests/fixtures/expected/romanian_contacts_cleaned.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
